--- a/runs/demo-cmp/testcases.xlsx
+++ b/runs/demo-cmp/testcases.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">本文テキスト（正規化）が不一致　【本文テキスト】N「: 牛乳を買う / レポート提出」→ N+1「フィルタなのに完了が表示: 部屋の掃除(完了)」</t>
+          <t xml:space="preserve">本文テキスト（正規化）が不一致　【本文テキスト】N「牛乳を買う / レポート提出」→ N+1「部屋の掃除(完了)」</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">本文テキスト（正規化）が不一致　【本文テキスト】N「'm done!」→ N+1「m done!  （アポストロフィ「'」が除去される）」</t>
+          <t xml:space="preserve">本文テキスト（正規化）が不一致　【本文テキスト】N「'」→ N+1「∅」</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">本文テキスト（正規化）が不一致　【本文テキスト】N「 B」→ N+1「amp; B  （実体参照がそのまま見える＝二重エスケープ）」</t>
+          <t xml:space="preserve">本文テキスト（正規化）が不一致　【本文テキスト】N「∅」→ N+1「amp;」</t>
         </is>
       </c>
     </row>

--- a/runs/demo-cmp/testcases.xlsx
+++ b/runs/demo-cmp/testcases.xlsx
@@ -103,7 +103,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -318,7 +318,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">期待結果(N観測)</t>
+          <t xml:space="preserve">期待結果（あるべき値／1回目Nを正とする）</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -370,7 +370,15 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL:https://uedakazuki-plainliving.github.io/auto-test-site-demo/normal/ / HTTP:200 / API:0件</t>
+          <t xml:space="preserve">【目的】トップ表示：初期ToDo一覧が表示される
+修正後(N+1)が下記のとおり1回目(N)と一致すること：
+・画面タイトル＝「ToDo管理」であること
+・主な見出し＝「ToDo管理」が表示されること
+・本文に「ToDo一覧: 牛乳を買う / レポート提出 / 部屋の掃除(完了)」が含まれること
+・入力フォーム＝1個が存在すること
+・HTTPステータス＝200（正常到達）で応答すること
+・画面表示（スクショ）が1回目と一致すること（画素差は判定感度の閾値内、コンソールエラーなし）
+※日時/ID/UUID/桁数の大きい数値など動的値の違いは判定感度に応じて無視されます（誤検知抑制）。</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -422,7 +430,15 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL:https://uedakazuki-plainliving.github.io/auto-test-site-demo/normal/ / HTTP:200 / API:0件</t>
+          <t xml:space="preserve">【目的】新規ToDoを追加できる
+修正後(N+1)が下記のとおり1回目(N)と一致すること：
+・画面タイトル＝「ToDo管理」であること
+・主な見出し＝「ToDo管理」が表示されること
+・本文に「ToDo一覧: 牛乳を買う / レポート提出 / 買い物に行く / 部屋の掃除(完了)」が含まれること
+・入力フォーム＝1個が存在すること
+・HTTPステータス＝200（正常到達）で応答すること
+・画面表示（スクショ）が1回目と一致すること（画素差は判定感度の閾値内、コンソールエラーなし）
+※日時/ID/UUID/桁数の大きい数値など動的値の違いは判定感度に応じて無視されます（誤検知抑制）。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -474,7 +490,15 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL:https://uedakazuki-plainliving.github.io/auto-test-site-demo/normal/ / HTTP:200 / API:0件</t>
+          <t xml:space="preserve">【目的】ToDoを完了にする（チェック）
+修正後(N+1)が下記のとおり1回目(N)と一致すること：
+・画面タイトル＝「ToDo管理」であること
+・主な見出し＝「ToDo管理」が表示されること
+・本文に「牛乳を買う(完了) / レポート提出 / 部屋の掃除(完了)」が含まれること
+・入力フォーム＝1個が存在すること
+・HTTPステータス＝200（正常到達）で応答すること
+・画面表示（スクショ）が1回目と一致すること（画素差は判定感度の閾値内、コンソールエラーなし）
+※日時/ID/UUID/桁数の大きい数値など動的値の違いは判定感度に応じて無視されます（誤検知抑制）。</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -526,7 +550,15 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL:https://uedakazuki-plainliving.github.io/auto-test-site-demo/normal/ / HTTP:200 / API:0件</t>
+          <t xml:space="preserve">【目的】ToDoを削除できる
+修正後(N+1)が下記のとおり1回目(N)と一致すること：
+・画面タイトル＝「ToDo管理」であること
+・主な見出し＝「ToDo管理」が表示されること
+・本文に「ToDo一覧: 牛乳を買う / 部屋の掃除(完了)」が含まれること
+・入力フォーム＝1個が存在すること
+・HTTPステータス＝200（正常到達）で応答すること
+・画面表示（スクショ）が1回目と一致すること（画素差は判定感度の閾値内、コンソールエラーなし）
+※日時/ID/UUID/桁数の大きい数値など動的値の違いは判定感度に応じて無視されます（誤検知抑制）。</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -578,7 +610,15 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL:https://uedakazuki-plainliving.github.io/auto-test-site-demo/normal/ / HTTP:200 / API:0件</t>
+          <t xml:space="preserve">【目的】「すべて」フィルタで全件表示
+修正後(N+1)が下記のとおり1回目(N)と一致すること：
+・画面タイトル＝「ToDo管理」であること
+・主な見出し＝「ToDo管理」が表示されること
+・本文に「全件: 牛乳を買う / レポート提出 / 部屋の掃除(完了)」が含まれること
+・入力フォーム＝1個が存在すること
+・HTTPステータス＝200（正常到達）で応答すること
+・画面表示（スクショ）が1回目と一致すること（画素差は判定感度の閾値内、コンソールエラーなし）
+※日時/ID/UUID/桁数の大きい数値など動的値の違いは判定感度に応じて無視されます（誤検知抑制）。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -630,7 +670,15 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL:https://uedakazuki-plainliving.github.io/auto-test-site-demo/normal/ / HTTP:200 / API:0件</t>
+          <t xml:space="preserve">【目的】「完了」フィルタで完了のみ表示
+修正後(N+1)が下記のとおり1回目(N)と一致すること：
+・画面タイトル＝「ToDo管理」であること
+・主な見出し＝「ToDo管理」が表示されること
+・本文に「完了: 部屋の掃除(完了)」が含まれること
+・入力フォーム＝1個が存在すること
+・HTTPステータス＝200（正常到達）で応答すること
+・画面表示（スクショ）が1回目と一致すること（画素差は判定感度の閾値内、コンソールエラーなし）
+※日時/ID/UUID/桁数の大きい数値など動的値の違いは判定感度に応じて無視されます（誤検知抑制）。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -682,7 +730,15 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL:https://uedakazuki-plainliving.github.io/auto-test-site-demo/normal/ / HTTP:200 / API:0件</t>
+          <t xml:space="preserve">【目的】「未完了」フィルタで未完了のみ表示
+修正後(N+1)が下記のとおり1回目(N)と一致すること：
+・画面タイトル＝「ToDo管理」であること
+・主な見出し＝「ToDo管理」が表示されること
+・本文に「未完了: 牛乳を買う / レポート提出」が含まれること
+・入力フォーム＝1個が存在すること
+・HTTPステータス＝200（正常到達）で応答すること
+・画面表示（スクショ）が1回目と一致すること（画素差は判定感度の閾値内、コンソールエラーなし）
+※日時/ID/UUID/桁数の大きい数値など動的値の違いは判定感度に応じて無視されます（誤検知抑制）。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -734,7 +790,15 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL:https://uedakazuki-plainliving.github.io/auto-test-site-demo/normal/ / HTTP:200 / API:0件</t>
+          <t xml:space="preserve">【目的】記号を含むToDo「I'm done!」を追加
+修正後(N+1)が下記のとおり1回目(N)と一致すること：
+・画面タイトル＝「ToDo管理」であること
+・主な見出し＝「ToDo管理」が表示されること
+・本文に「追加結果: I'm done!」が含まれること
+・入力フォーム＝1個が存在すること
+・HTTPステータス＝200（正常到達）で応答すること
+・画面表示（スクショ）が1回目と一致すること（画素差は判定感度の閾値内、コンソールエラーなし）
+※日時/ID/UUID/桁数の大きい数値など動的値の違いは判定感度に応じて無視されます（誤検知抑制）。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -786,7 +850,15 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL:https://uedakazuki-plainliving.github.io/auto-test-site-demo/normal/ / HTTP:200 / API:0件</t>
+          <t xml:space="preserve">【目的】「A &amp; B」を追加して一覧表示
+修正後(N+1)が下記のとおり1回目(N)と一致すること：
+・画面タイトル＝「ToDo管理」であること
+・主な見出し＝「ToDo管理」が表示されること
+・本文に「表示結果: A &amp; B」が含まれること
+・入力フォーム＝1個が存在すること
+・HTTPステータス＝200（正常到達）で応答すること
+・画面表示（スクショ）が1回目と一致すること（画素差は判定感度の閾値内、コンソールエラーなし）
+※日時/ID/UUID/桁数の大きい数値など動的値の違いは判定感度に応じて無視されます（誤検知抑制）。</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -838,7 +910,15 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">URL:https://uedakazuki-plainliving.github.io/auto-test-site-demo/normal/ / HTTP:200 / API:0件</t>
+          <t xml:space="preserve">【目的】空入力の送信は拒否される
+修正後(N+1)が下記のとおり1回目(N)と一致すること：
+・画面タイトル＝「ToDo管理」であること
+・主な見出し＝「ToDo管理」が表示されること
+・本文に「空入力は無視され件数は変わらない」が含まれること
+・入力フォーム＝1個が存在すること
+・HTTPステータス＝200（正常到達）で応答すること
+・画面表示（スクショ）が1回目と一致すること（画素差は判定感度の閾値内、コンソールエラーなし）
+※日時/ID/UUID/桁数の大きい数値など動的値の違いは判定感度に応じて無視されます（誤検知抑制）。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/runs/demo-cmp/testcases.xlsx
+++ b/runs/demo-cmp/testcases.xlsx
@@ -45,7 +45,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -55,7 +55,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
